--- a/duoki_editor/resources/data/blank/服装店-自由画画-3-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-自由画画-3-blank.xlsx
@@ -121,34 +121,34 @@
     <t>{user_name}设计师，我们快来看看吧！</t>
   </si>
   <si>
-    <t>请先把橙色边框的短袖上衣放在玩偶上半身吧，准备开始设计啦！</t>
-  </si>
-  <si>
-    <t>快把橙色边框的短袖上衣放在玩偶上半身吧！</t>
-  </si>
-  <si>
-    <t>时间快来不及了！把橙色边框的短袖上衣放在玩偶上半身吧！</t>
+    <t>请先把橙色边框的T恤衫放在玩偶上半身吧，准备开始设计啦！</t>
+  </si>
+  <si>
+    <t>快把橙色边框的T恤衫放在玩偶上半身吧！</t>
+  </si>
+  <si>
+    <t>时间快来不及了！把橙色边框的T恤衫放在玩偶上半身吧！</t>
   </si>
   <si>
     <t>200403|200435</t>
   </si>
   <si>
-    <t>魔镜出来啦！你可以照着图案画，或者画自己想要的图形哦！</t>
-  </si>
-  <si>
-    <t>画完了把衣服放在魔镜上吧！</t>
-  </si>
-  <si>
-    <t>时间不多了，再不放在魔镜上，他就要没有魔力了！</t>
-  </si>
-  <si>
-    <t>不好啦，魔镜的魔力消失了，我们下次再来设计衣服吧！</t>
+    <t>魔镜出来啦！你可以照着图案画，或者画自己想要的图案哦！</t>
+  </si>
+  <si>
+    <t>画完了把T恤衫放在魔镜上吧！</t>
+  </si>
+  <si>
+    <t>时间不多了，再不放在魔镜上，它就要没有魔力了！</t>
+  </si>
+  <si>
+    <t>不好啦，魔镜的魔力消失了，我们下次再来设计吧！</t>
   </si>
   <si>
     <t>画完了就点一下屏幕上的按钮哟！</t>
   </si>
   <si>
-    <t>哈哈，我已经帮你把你画的图案变到衣服上了！</t>
+    <t>哈哈，我已经帮你把你画的图案变到T恤衫上了！</t>
   </si>
   <si>
     <t>你可以告诉我你画的是什么吗？比如他是什么东西？他是什么颜色之类的。</t>
@@ -157,7 +157,7 @@
     <t>对了{user_name}，我们使用多奇能力，把他变成你想要的样子吧！让我们一起说，哇塞！多奇！你好神奇！</t>
   </si>
   <si>
-    <t>我帮你把这个衣服用魔法拍照下来存在你的服装店里吧！</t>
+    <t>我帮你把这件T恤衫用魔法拍照下来存在你的服装店里吧！</t>
   </si>
   <si>
     <t>200401</t>
